--- a/human_resources_surveys/026_hr_reputation_perception_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/026_hr_reputation_perception_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2.2,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2.2, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2.3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2.3, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2.4,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2.4, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'label':_'definitely'}</t>
+          <t>definitely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'label': 'Definitely'}</t>
+          <t>Definitely</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'label': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'label': 'Not very likely'}</t>
+          <t>Not very likely</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4.4,_'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4.4, 'label': 'Not at all likely'}</t>
+          <t>Not at all likely</t>
         </is>
       </c>
     </row>
